--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_03-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_03-10-2025.xlsx
@@ -544,12 +544,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£11.17</t>
+          <t>£10.35</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£11.17</t>
+          <t>£10.35</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£10.48</t>
+          <t>£10.13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -666,12 +666,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£13.30</t>
+          <t>£11.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£13.30</t>
+          <t>£11.65</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>£11.63</t>
+          <t>£11.44</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -788,12 +788,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£15.95</t>
+          <t>£15.10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£15.95</t>
+          <t>£15.10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>£15.07</t>
+          <t>£14.78</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -910,12 +910,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£16.95</t>
+          <t>£15.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£16.95</t>
+          <t>£15.40</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£15.56</t>
+          <t>£15.08</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£21.50</t>
+          <t>£19.60</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£21.50</t>
+          <t>£19.60</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>£19.56</t>
+          <t>£19.18</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£23.95</t>
+          <t>£21.35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£23.95</t>
+          <t>£21.35</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£21.32</t>
+          <t>£20.92</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1276,19 +1276,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>£21.55</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>£21.55</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>£23.50</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>£23.50</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>£23.50</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>£21.58</t>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£21.51</t>
+          <t>£21.12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£26.95</t>
+          <t>£24.75</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£26.95</t>
+          <t>£24.75</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>£24.97</t>
+          <t>£24.25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£28.95</t>
+          <t>£26.80</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£28.95</t>
+          <t>£26.80</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>£26.75</t>
+          <t>£26.28</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£28.95</t>
+          <t>£26.20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£28.95</t>
+          <t>£26.20</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£26.45</t>
+          <t>£25.94</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1764,12 +1764,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£37.95</t>
+          <t>£35.13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>£37.95</t>
+          <t>£35.13</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>£35.49</t>
+          <t>£35.45</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1886,12 +1886,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£34.95</t>
+          <t>£32.35</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£34.95</t>
+          <t>£32.35</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>£32.29</t>
+          <t>£31.72</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2008,12 +2008,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£42.50</t>
+          <t>£39.76</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£42.50</t>
+          <t>£39.76</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£39.68</t>
+          <t>£39.76</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£42.95</t>
+          <t>£40.39</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£40.31</t>
+          <t>£39.05</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2251,12 +2251,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£44.95</t>
+          <t>£39.99</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£44.95</t>
+          <t>£39.99</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£39.42</t>
+          <t>£38.66</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2373,12 +2373,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>£729.95</t>
+          <t>£695.00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>£729.95</t>
+          <t>£695.00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>£935.40</t>
+          <t>£895.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>£935.40</t>
+          <t>£895.00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>£29.52</t>
+          <t>£28.99</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>£35.64</t>
+          <t>£34.64</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>£39.81</t>
+          <t>£40.21</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>£44.07</t>
+          <t>£44.52</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>£43.70</t>
+          <t>£43.99</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>£43.30</t>
+          <t>£43.69</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>£42.90</t>
+          <t>£43.14</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bd351eb5+80197]
-	GetHandleVerifier [0x0x7ff6bd351f10+80288]
-	(No symbol) [0x0x7ff6bd0d02fa]
-	(No symbol) [0x0x7ff6bd127cd7]
-	(No symbol) [0x0x7ff6bd127f9c]
-	(No symbol) [0x0x7ff6bd17ba87]
-	(No symbol) [0x0x7ff6bd1503bf]
-	(No symbol) [0x0x7ff6bd1787fb]
-	(No symbol) [0x0x7ff6bd150153]
-	(No symbol) [0x0x7ff6bd118b02]
-	(No symbol) [0x0x7ff6bd1198d3]
-	GetHandleVerifier [0x0x7ff6bd60e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bd608c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bd6286c7+3055959]
-	GetHandleVerifier [0x0x7ff6bd36cfee+191102]
-	GetHandleVerifier [0x0x7ff6bd3750af+224063]
-	GetHandleVerifier [0x0x7ff6bd35af64+117236]
-	GetHandleVerifier [0x0x7ff6bd35b119+117673]
-	GetHandleVerifier [0x0x7ff6bd3410a8+11064]
+	GetHandleVerifier [0x0x7ff768bb1eb5+80197]
+	GetHandleVerifier [0x0x7ff768bb1f10+80288]
+	(No symbol) [0x0x7ff7689302fa]
+	(No symbol) [0x0x7ff768987cd7]
+	(No symbol) [0x0x7ff768987f9c]
+	(No symbol) [0x0x7ff7689dba87]
+	(No symbol) [0x0x7ff7689b03bf]
+	(No symbol) [0x0x7ff7689d87fb]
+	(No symbol) [0x0x7ff7689b0153]
+	(No symbol) [0x0x7ff768978b02]
+	(No symbol) [0x0x7ff7689798d3]
+	GetHandleVerifier [0x0x7ff768e6e83d+2949837]
+	GetHandleVerifier [0x0x7ff768e68c6a+2926330]
+	GetHandleVerifier [0x0x7ff768e886c7+3055959]
+	GetHandleVerifier [0x0x7ff768bccfee+191102]
+	GetHandleVerifier [0x0x7ff768bd50af+224063]
+	GetHandleVerifier [0x0x7ff768bbaf64+117236]
+	GetHandleVerifier [0x0x7ff768bbb119+117673]
+	GetHandleVerifier [0x0x7ff768ba10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
